--- a/pruebas/cañar_TVpromediostotal.xlsx
+++ b/pruebas/cañar_TVpromediostotal.xlsx
@@ -856,14 +856,20 @@
       <c r="Z9" s="7" t="n">
         <v>54.75</v>
       </c>
-      <c r="AA9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="7" t="n">
-        <v>0</v>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD9" s="7" t="n">
         <v>52.19</v>
@@ -964,14 +970,20 @@
       <c r="Z10" s="7" t="n">
         <v>62.26</v>
       </c>
-      <c r="AA10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="7" t="n">
-        <v>0</v>
+      <c r="AA10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD10" s="7" t="n">
         <v>62.62</v>
@@ -1072,14 +1084,20 @@
       <c r="Z11" s="7" t="n">
         <v>28.12</v>
       </c>
-      <c r="AA11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="7" t="n">
-        <v>0</v>
+      <c r="AA11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD11" s="7" t="n">
         <v>27.18</v>
@@ -1180,14 +1198,20 @@
       <c r="Z12" s="7" t="n">
         <v>46.78</v>
       </c>
-      <c r="AA12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="7" t="n">
-        <v>0</v>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD12" s="7" t="n">
         <v>45.82</v>
@@ -1288,14 +1312,20 @@
       <c r="Z13" s="7" t="n">
         <v>20.75</v>
       </c>
-      <c r="AA13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="7" t="n">
-        <v>0</v>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD13" s="7" t="n">
         <v>20.72</v>
@@ -1396,14 +1426,20 @@
       <c r="Z14" s="7" t="n">
         <v>16.9</v>
       </c>
-      <c r="AA14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="7" t="n">
-        <v>0</v>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD14" s="7" t="n">
         <v>16.85</v>
@@ -1504,14 +1540,20 @@
       <c r="Z15" s="7" t="n">
         <v>28.28</v>
       </c>
-      <c r="AA15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="7" t="n">
-        <v>0</v>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD15" s="7" t="n">
         <v>28.19</v>
@@ -1612,14 +1654,20 @@
       <c r="Z16" s="7" t="n">
         <v>21.79</v>
       </c>
-      <c r="AA16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="7" t="n">
-        <v>0</v>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD16" s="7" t="n">
         <v>20.5</v>
@@ -1720,14 +1768,20 @@
       <c r="Z17" s="7" t="n">
         <v>18.21</v>
       </c>
-      <c r="AA17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="7" t="n">
-        <v>0</v>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD17" s="7" t="n">
         <v>18.28</v>
@@ -1828,14 +1882,20 @@
       <c r="Z18" s="10" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="10" t="n">
-        <v>0</v>
+      <c r="AA18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD18" s="10" t="n">
         <v>17.28</v>
